--- a/exam_forms/021_ent_knowledge_quiz--exam_forms.xlsx
+++ b/exam_forms/021_ent_knowledge_quiz--exam_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,18 +520,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>form_1_name</t>
+          <t>question_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>form-1-name</t>
+          <t>What is the primary function of the Endotracheal Tube (ET) in the management of a patient with a tracheal injury?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,18 +543,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>form_1_question</t>
+          <t>question_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>form-1-question</t>
+          <t>How does the Endotracheal Tube (ET) affect the pressure of the trachea?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,18 +566,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>form_1_question_0</t>
+          <t>question_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>question 1</t>
+          <t>What are the indications for the use of the Endotracheal Tube?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,41 +589,41 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>form_1_question_1</t>
+          <t>question_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>question 2</t>
+          <t>What are the complications associated with the Endotracheal Tube?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>form_1_scale_question_1</t>
+          <t>question_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>question 3 scale</t>
+          <t>What are the common causes of the Endotracheal Tube obstruction?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,41 +635,41 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>form_1_scale_1_question_1</t>
+          <t>question_6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>question-3 scale</t>
+          <t>How does the Endotracheal Tube affect the patient's oxygenation?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>form_1_email</t>
+          <t>question_7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>What is the preferred method of securing the Endotracheal Tube in the ICU?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,18 +681,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>form_1_phone</t>
+          <t>question_8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>What are the signs and symptoms of the Endotracheal Tube malfunction?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,18 +704,18 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>form_2_name</t>
+          <t>question_9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>form-2-name</t>
+          <t>How does the Endotracheal Tube impact the patient's comfort level?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,87 +727,87 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>form_2_question</t>
+          <t>question_10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>form-2-question</t>
+          <t>What is the role of the Endotracheal Tube in the management of a patient with a trachea injury?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>form_2_question_0</t>
+          <t>question_11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>question 1</t>
+          <t>What are the post-procedure complications of the Endotracheal Tube insertion?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>form_2_question_1</t>
+          <t>question_12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>question 2</t>
+          <t>What are the post-procedure complications of the Endotracheal Tube removal?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>form_2_scale_question_1</t>
+          <t>question_13</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>question 2 scale</t>
+          <t>What are the steps to follow in case of an Endotracheal Tube malfunction?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -819,18 +819,18 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>form_2_scale_1_question_1</t>
+          <t>question_14</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>question 2 scale</t>
+          <t>What is the recommended approach for securing the Endotracheal Tube?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -842,18 +842,18 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>form_2_email</t>
+          <t>question_15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>What is the most common cause of the Endotracheal Tube obstruction?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -865,18 +865,64 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>form_2_phone</t>
+          <t>question_16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>Question 16</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>question_17</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Question 17</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>question_18</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>What is the recommended method for the Endotracheal Tube insertion and removal?</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -894,9 +940,9 @@
   <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -919,204 +965,204 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>form_1_question_0_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'option-1'}</t>
+          <t>airway_obstruction</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'option-1'}</t>
+          <t>Airway obstruction</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>form_1_question_0_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'option-2'}</t>
+          <t>cardiac_arrest</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'option-2'}</t>
+          <t>Cardiac arrest</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>form_1_question_0_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'option-3'}</t>
+          <t>respiratory_failure</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'option-3'}</t>
+          <t>Respiratory failure</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>form_1_question_1_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'option-1'}</t>
+          <t>pneumothorax</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'option-1'}</t>
+          <t>Pneumothorax</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>form_1_question_1_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'option-2'}</t>
+          <t>tracheal_damage</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'option-2'}</t>
+          <t>Tracheal damage</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>form_1_question_1_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'option-3'}</t>
+          <t>cardiac_arrest</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'option-3'}</t>
+          <t>Cardiac arrest</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>form_2_question_0_choices</t>
+          <t>question_7_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'option-1'}</t>
+          <t>tape</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'option-1'}</t>
+          <t>Tape</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>form_2_question_0_choices</t>
+          <t>question_7_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'option-2'}</t>
+          <t>adhesive</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'option-2'}</t>
+          <t>Adhesive</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>form_2_question_0_choices</t>
+          <t>question_7_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'option-3'}</t>
+          <t>umbilical_tape</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'option-3'}</t>
+          <t>Umbilical tape</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>form_2_question_1_choices</t>
+          <t>question_18_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'option-1'}</t>
+          <t>bronchoscope</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'option-1'}</t>
+          <t>Bronchoscope</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>form_2_question_1_choices</t>
+          <t>question_18_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'option-2'}</t>
+          <t>fibre_optic_bronchoscope</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'option-2'}</t>
+          <t>Fibre Optic bronchoscope</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>form_2_question_1_choices</t>
+          <t>question_18_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'option-3'}</t>
+          <t>nasal_tube</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'option-3'}</t>
+          <t>Nasal tube</t>
         </is>
       </c>
     </row>
